--- a/Delhi-May-2025.xlsx
+++ b/Delhi-May-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="75">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Delhi</t>
   </si>
   <si>
@@ -106,10 +109,10 @@
     <t>MH02FG7557</t>
   </si>
   <si>
-    <t>DL1NA-3869</t>
-  </si>
-  <si>
-    <t>DL1NA-3910</t>
+    <t>DL1NA3869</t>
+  </si>
+  <si>
+    <t>DL1NA3910</t>
   </si>
   <si>
     <t>HR38AD1176</t>
@@ -130,13 +133,13 @@
     <t>HR38AE5738</t>
   </si>
   <si>
-    <t>HR38Y-6988</t>
-  </si>
-  <si>
-    <t>HR55AR-0857</t>
-  </si>
-  <si>
-    <t>HR55AR-1793</t>
+    <t>HR38Y6988</t>
+  </si>
+  <si>
+    <t>HR55AR0857</t>
+  </si>
+  <si>
+    <t>HR55AR1793</t>
   </si>
   <si>
     <t>MH02ER7925</t>
@@ -154,7 +157,7 @@
     <t>MH02FG5537</t>
   </si>
   <si>
-    <t>DL1N-6505</t>
+    <t>DL1N6505</t>
   </si>
   <si>
     <t>HR38AE9224</t>
@@ -184,7 +187,7 @@
     <t>CAMRY</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>ETIOS</t>
@@ -200,6 +203,39 @@
   </si>
   <si>
     <t>URBANIA</t>
+  </si>
+  <si>
+    <t>25/01/2024</t>
+  </si>
+  <si>
+    <t>17/08/2022</t>
+  </si>
+  <si>
+    <t>21/04/2023</t>
+  </si>
+  <si>
+    <t>16/08/2018</t>
+  </si>
+  <si>
+    <t>28/11/2023</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>21/09/2021</t>
+  </si>
+  <si>
+    <t>21/10/2021</t>
+  </si>
+  <si>
+    <t>21/04/2014</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>23/01/2025</t>
   </si>
   <si>
     <t>-</t>
@@ -209,6 +245,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -261,11 +300,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,10 +600,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -642,28 +682,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2">
-        <v>45316</v>
+        <v>55</v>
+      </c>
+      <c r="G2" t="s">
+        <v>63</v>
       </c>
       <c r="H2">
         <v>45360</v>
@@ -723,27 +766,27 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3">
-        <v>44719</v>
+        <v>56</v>
+      </c>
+      <c r="G3" s="2">
+        <v>44748</v>
       </c>
       <c r="H3">
         <v>28902</v>
@@ -803,27 +846,27 @@
         <v>-198.54</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="G4" s="2">
+        <v>43565</v>
       </c>
       <c r="H4">
         <v>211561</v>
@@ -883,27 +926,27 @@
         <v>48.88</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="G5" s="2">
+        <v>43565</v>
       </c>
       <c r="H5">
         <v>212395</v>
@@ -963,27 +1006,27 @@
         <v>36.83</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
-        <v>44790</v>
+        <v>57</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
       </c>
       <c r="H6">
         <v>194058</v>
@@ -1043,27 +1086,27 @@
         <v>49.13</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
-        <v>44816</v>
+        <v>57</v>
+      </c>
+      <c r="G7" s="2">
+        <v>44904</v>
       </c>
       <c r="H7">
         <v>122127</v>
@@ -1123,27 +1166,27 @@
         <v>35.04</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
-        <v>44790</v>
+        <v>57</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
       </c>
       <c r="H8">
         <v>150983</v>
@@ -1203,27 +1246,27 @@
         <v>53.13</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>44816</v>
+        <v>57</v>
+      </c>
+      <c r="G9" s="2">
+        <v>44904</v>
       </c>
       <c r="H9">
         <v>131335</v>
@@ -1283,27 +1326,27 @@
         <v>45.9</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
-        <v>45037</v>
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>65</v>
       </c>
       <c r="H10">
         <v>102724</v>
@@ -1363,27 +1406,27 @@
         <v>8.23</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
-        <v>45037</v>
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
       </c>
       <c r="H11">
         <v>99930</v>
@@ -1443,27 +1486,27 @@
         <v>8.84</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H12">
         <v>113705</v>
@@ -1523,27 +1566,27 @@
         <v>61.54</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H13">
         <v>73719</v>
@@ -1603,27 +1646,27 @@
         <v>19.14</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H14">
         <v>88355</v>
@@ -1683,27 +1726,27 @@
         <v>24.11</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="G15" s="2">
+        <v>43587</v>
       </c>
       <c r="H15">
         <v>177537</v>
@@ -1763,27 +1806,27 @@
         <v>48.14</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
-        <v>44236</v>
+        <v>57</v>
+      </c>
+      <c r="G16" s="2">
+        <v>44441</v>
       </c>
       <c r="H16">
         <v>100143</v>
@@ -1848,22 +1891,22 @@
         <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17">
-        <v>44280</v>
+        <v>57</v>
+      </c>
+      <c r="G17" t="s">
+        <v>68</v>
       </c>
       <c r="H17">
         <v>79522</v>
@@ -1928,22 +1971,22 @@
         <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>44460</v>
+        <v>57</v>
+      </c>
+      <c r="G18" t="s">
+        <v>69</v>
       </c>
       <c r="H18">
         <v>93057</v>
@@ -2008,22 +2051,22 @@
         <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19">
-        <v>44490</v>
+        <v>57</v>
+      </c>
+      <c r="G19" t="s">
+        <v>70</v>
       </c>
       <c r="H19">
         <v>76163</v>
@@ -2088,22 +2131,22 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2160,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="Z20" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:26">
@@ -2168,22 +2211,22 @@
         <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21">
-        <v>44999</v>
+        <v>59</v>
+      </c>
+      <c r="G21" t="s">
+        <v>72</v>
       </c>
       <c r="H21">
         <v>99392</v>
@@ -2248,22 +2291,22 @@
         <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22">
-        <v>45293</v>
+        <v>60</v>
+      </c>
+      <c r="G22" s="2">
+        <v>45323</v>
       </c>
       <c r="H22">
         <v>32875</v>
@@ -2328,22 +2371,22 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <v>45510</v>
+        <v>61</v>
+      </c>
+      <c r="G23" s="2">
+        <v>45451</v>
       </c>
       <c r="H23">
         <v>24459</v>
@@ -2408,22 +2451,22 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24">
-        <v>45510</v>
+        <v>61</v>
+      </c>
+      <c r="G24" s="2">
+        <v>45451</v>
       </c>
       <c r="H24">
         <v>26962</v>
@@ -2488,22 +2531,22 @@
         <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>45481</v>
+        <v>61</v>
+      </c>
+      <c r="G25" s="2">
+        <v>45511</v>
       </c>
       <c r="H25">
         <v>28663</v>
@@ -2568,22 +2611,22 @@
         <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26">
-        <v>45481</v>
+        <v>61</v>
+      </c>
+      <c r="G26" s="2">
+        <v>45511</v>
       </c>
       <c r="H26">
         <v>30373</v>
@@ -2648,22 +2691,22 @@
         <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27">
-        <v>45680</v>
+        <v>62</v>
+      </c>
+      <c r="G27" t="s">
+        <v>73</v>
       </c>
       <c r="H27">
         <v>3941</v>
